--- a/results/human_health_breakdown/2025/propanol production, biogas, green ethylene.xlsx
+++ b/results/human_health_breakdown/2025/propanol production, biogas, green ethylene.xlsx
@@ -444,7 +444,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>4.072363390644084E-06</v>
+        <v>4.026721763861525E-06</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>4.830522535265923E-08</v>
+        <v>3.075782218608224E-09</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>2.893242006293765E-10</v>
+        <v>8.310456313939641E-12</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>1.365382654834001E-10</v>
+        <v>5.366841751465054E-12</v>
       </c>
       <c r="E9">
         <v>1</v>
